--- a/uploads/PhonesSample.xlsx
+++ b/uploads/PhonesSample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Git Project\Warehouse\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ALLAH\Warehouse\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C3E0C9-E1A7-47A0-8AF8-2CD42F9EA8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC9A701-62F1-48D4-90BF-3A35861B3FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30630" yWindow="1830" windowWidth="15300" windowHeight="7725" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,9 +30,6 @@
     <t>username</t>
   </si>
   <si>
-    <t>project</t>
-  </si>
-  <si>
     <t>phone_number</t>
   </si>
   <si>
@@ -42,13 +39,16 @@
     <t>نام کاربری</t>
   </si>
   <si>
-    <t>پروژه</t>
-  </si>
-  <si>
     <t>شماره تلفن</t>
   </si>
   <si>
     <t>پیش شماره</t>
+  </si>
+  <si>
+    <t>مکان</t>
+  </si>
+  <si>
+    <t>place</t>
   </si>
 </sst>
 </file>
@@ -408,40 +408,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
